--- a/error_input.xlsx
+++ b/error_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plumx\git_rep\ai_check_bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FAAB90-2237-4AB3-89E1-12AD1650E23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C6A670-273C-4C76-849A-7D7889935A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,11 +83,34 @@
     <t>スペースを補完しました。</t>
   </si>
   <si>
-    <t>予算</t>
+    <t>担当者名,予算</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>担当者名,予算</t>
+    <r>
+      <t>予算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ステータス</t>
+    </r>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -95,7 +118,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,6 +147,13 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -508,7 +538,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -520,7 +550,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -528,7 +558,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
